--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109888420</v>
+        <v>109913951</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543030.4168770119</v>
+        <v>543346</v>
       </c>
       <c r="R2" t="n">
-        <v>6966641.675278639</v>
+        <v>6966508</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109888419</v>
+        <v>109913928</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542965.6125551963</v>
+        <v>543112</v>
       </c>
       <c r="R3" t="n">
-        <v>6966626.655574583</v>
+        <v>6966535</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109888421</v>
+        <v>109913933</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543044.8905910169</v>
+        <v>543213</v>
       </c>
       <c r="R4" t="n">
-        <v>6966689.861451562</v>
+        <v>6966455</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109888422</v>
+        <v>109913954</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543044.8905910169</v>
+        <v>543314</v>
       </c>
       <c r="R5" t="n">
-        <v>6966689.861451562</v>
+        <v>6966453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109888418</v>
+        <v>109913958</v>
       </c>
       <c r="B6" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,38 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542988.5742467908</v>
+        <v>543107</v>
       </c>
       <c r="R6" t="n">
-        <v>6966621.013854409</v>
+        <v>6966352</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,24 +1131,9 @@
           <t>2023-06-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>några år gammalt ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109914094</v>
+        <v>109913930</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543258.9788421572</v>
+        <v>543234</v>
       </c>
       <c r="R7" t="n">
-        <v>6966422.516919451</v>
+        <v>6966533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,19 +1228,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,12 +1260,7 @@
         <v>109913947</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543320.8309782374</v>
+        <v>543321</v>
       </c>
       <c r="R8" t="n">
-        <v>6966592.014229868</v>
+        <v>6966592</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,19 +1325,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109914113</v>
+        <v>109913950</v>
       </c>
       <c r="B9" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543022.025902151</v>
+        <v>543346</v>
       </c>
       <c r="R9" t="n">
-        <v>6966513.571636075</v>
+        <v>6966508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109914096</v>
+        <v>109913929</v>
       </c>
       <c r="B10" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543258.9788421572</v>
+        <v>543147</v>
       </c>
       <c r="R10" t="n">
-        <v>6966422.516919451</v>
+        <v>6966715</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,19 +1519,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109913949</v>
+        <v>109913935</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543345.7534210099</v>
+        <v>543223</v>
       </c>
       <c r="R11" t="n">
-        <v>6966507.31807487</v>
+        <v>6966400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,19 +1616,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109913935</v>
+        <v>109913953</v>
       </c>
       <c r="B12" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543223.1090773517</v>
+        <v>543342</v>
       </c>
       <c r="R12" t="n">
-        <v>6966400.101333712</v>
+        <v>6966456</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1877,19 +1713,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,37 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109913934</v>
+        <v>109913931</v>
       </c>
       <c r="B13" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1956,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543188.9378444579</v>
+        <v>543175</v>
       </c>
       <c r="R13" t="n">
-        <v>6966422.508602787</v>
+        <v>6966528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,19 +1810,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,37 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109914108</v>
+        <v>109913948</v>
       </c>
       <c r="B14" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543345.7534210099</v>
+        <v>543329</v>
       </c>
       <c r="R14" t="n">
-        <v>6966507.31807487</v>
+        <v>6966529</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,19 +1907,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109913932</v>
+        <v>109888421</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2180,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543167.0957201822</v>
+        <v>543045</v>
       </c>
       <c r="R15" t="n">
-        <v>6966482.10628217</v>
+        <v>6966690</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2210,22 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,49 +2021,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109913937</v>
+        <v>109913936</v>
       </c>
       <c r="B16" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2292,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543258.9788421572</v>
+        <v>543259</v>
       </c>
       <c r="R16" t="n">
-        <v>6966422.516919451</v>
+        <v>6966422</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2325,19 +2101,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2364,37 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109914089</v>
+        <v>109913955</v>
       </c>
       <c r="B17" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2404,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543174.7268768897</v>
+        <v>543315</v>
       </c>
       <c r="R17" t="n">
-        <v>6966528.376882299</v>
+        <v>6966437</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2437,19 +2198,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109914109</v>
+        <v>109913959</v>
       </c>
       <c r="B18" t="n">
-        <v>89317</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543341.3888863667</v>
+        <v>543102</v>
       </c>
       <c r="R18" t="n">
-        <v>6966456.51847708</v>
+        <v>6966329</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2546,22 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2588,15 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109914098</v>
+        <v>109913939</v>
       </c>
       <c r="B19" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543267.577139626</v>
+        <v>543259</v>
       </c>
       <c r="R19" t="n">
-        <v>6966603.653762043</v>
+        <v>6966422</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,19 +2392,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,37 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109914105</v>
+        <v>109913940</v>
       </c>
       <c r="B20" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2740,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543328.5230237712</v>
+        <v>543268</v>
       </c>
       <c r="R20" t="n">
-        <v>6966529.489856509</v>
+        <v>6966603</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2773,19 +2489,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2812,15 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109914111</v>
+        <v>109913961</v>
       </c>
       <c r="B21" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,21 +2529,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2852,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543314.6379258774</v>
+        <v>543135</v>
       </c>
       <c r="R21" t="n">
-        <v>6966436.965395859</v>
+        <v>6966325</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2882,22 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,15 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109914115</v>
+        <v>109913934</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2940,21 +2626,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543102.2650683342</v>
+        <v>543189</v>
       </c>
       <c r="R22" t="n">
-        <v>6966329.482156066</v>
+        <v>6966423</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,22 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3036,15 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109914107</v>
+        <v>109913937</v>
       </c>
       <c r="B23" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3052,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3076,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543345.7534210099</v>
+        <v>543259</v>
       </c>
       <c r="R23" t="n">
-        <v>6966507.31807487</v>
+        <v>6966422</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3109,19 +2780,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,37 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109913928</v>
+        <v>109913943</v>
       </c>
       <c r="B24" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543111.4754650187</v>
+        <v>543268</v>
       </c>
       <c r="R24" t="n">
-        <v>6966534.402143236</v>
+        <v>6966603</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3221,19 +2877,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,15 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109913960</v>
+        <v>109913956</v>
       </c>
       <c r="B25" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3300,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543135.2868897767</v>
+        <v>543022</v>
       </c>
       <c r="R25" t="n">
-        <v>6966324.887347969</v>
+        <v>6966513</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3333,19 +2974,9 @@
           <t>2023-06-07</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,15 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109913954</v>
+        <v>109888420</v>
       </c>
       <c r="B26" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3412,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543313.5113610106</v>
+        <v>543030</v>
       </c>
       <c r="R26" t="n">
-        <v>6966452.950413501</v>
+        <v>6966641</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3442,22 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3472,49 +3088,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109913930</v>
+        <v>109913949</v>
       </c>
       <c r="B27" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3524,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543234.6301683459</v>
+        <v>543346</v>
       </c>
       <c r="R27" t="n">
-        <v>6966533.279773307</v>
+        <v>6966508</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3557,19 +3168,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3596,15 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109913939</v>
+        <v>109888418</v>
       </c>
       <c r="B28" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3612,34 +3208,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543258.9788421572</v>
+        <v>542989</v>
       </c>
       <c r="R28" t="n">
-        <v>6966422.516919451</v>
+        <v>6966621</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3666,22 +3266,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>några år gammalt ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3696,27 +3291,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109913942</v>
+        <v>109888419</v>
       </c>
       <c r="B29" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3724,21 +3314,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3748,10 +3338,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543267.577139626</v>
+        <v>542965</v>
       </c>
       <c r="R29" t="n">
-        <v>6966603.653762043</v>
+        <v>6966627</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3778,22 +3368,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3808,27 +3388,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109913933</v>
+        <v>109888422</v>
       </c>
       <c r="B30" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3836,21 +3411,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3860,10 +3435,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543212.7749056042</v>
+        <v>543045</v>
       </c>
       <c r="R30" t="n">
-        <v>6966454.822230591</v>
+        <v>6966690</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3890,22 +3465,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3920,27 +3485,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109914112</v>
+        <v>109913938</v>
       </c>
       <c r="B31" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3948,21 +3508,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3972,10 +3532,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543022.025902151</v>
+        <v>543259</v>
       </c>
       <c r="R31" t="n">
-        <v>6966513.571636075</v>
+        <v>6966422</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4002,22 +3562,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4044,15 +3594,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109914114</v>
+        <v>109913941</v>
       </c>
       <c r="B32" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4060,21 +3605,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4084,10 +3629,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543107.0117672184</v>
+        <v>543268</v>
       </c>
       <c r="R32" t="n">
-        <v>6966351.487864901</v>
+        <v>6966603</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4114,22 +3659,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4156,15 +3691,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109914099</v>
+        <v>109913957</v>
       </c>
       <c r="B33" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4196,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543267.577139626</v>
+        <v>543022</v>
       </c>
       <c r="R33" t="n">
-        <v>6966603.653762043</v>
+        <v>6966513</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4226,22 +3756,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4268,15 +3788,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109913961</v>
+        <v>109913926</v>
       </c>
       <c r="B34" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4284,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4308,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543135.2868897767</v>
+        <v>543159</v>
       </c>
       <c r="R34" t="n">
-        <v>6966324.887347969</v>
+        <v>6966350</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4338,22 +3853,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4380,15 +3885,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109914085</v>
+        <v>109913942</v>
       </c>
       <c r="B35" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4420,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543158.757654801</v>
+        <v>543268</v>
       </c>
       <c r="R35" t="n">
-        <v>6966350.339414816</v>
+        <v>6966603</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4453,19 +3953,9 @@
           <t>2023-06-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,15 +3982,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109914087</v>
+        <v>109913960</v>
       </c>
       <c r="B36" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4508,21 +3993,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4532,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543147.5534001305</v>
+        <v>543135</v>
       </c>
       <c r="R36" t="n">
-        <v>6966714.979262992</v>
+        <v>6966325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4562,22 +4047,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4601,118 +4076,6 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>109913943</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Skalberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>543267.577139626</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6966603.653762043</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Hällesjö</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2023-06-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1839,45 +1839,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109913948</v>
+        <v>135533943</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>91995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skalberget, Jmt</t>
+          <t>Tallskogen, Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543329</v>
+        <v>543200</v>
       </c>
       <c r="R14" t="n">
-        <v>6966529</v>
+        <v>6966382</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1924,44 +1924,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109888421</v>
+        <v>109913948</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543045</v>
+        <v>543329</v>
       </c>
       <c r="R15" t="n">
-        <v>6966690</v>
+        <v>6966529</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2021,19 +2021,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109913936</v>
+        <v>109888421</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543259</v>
+        <v>543045</v>
       </c>
       <c r="R16" t="n">
-        <v>6966422</v>
+        <v>6966690</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2118,19 +2118,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109913955</v>
+        <v>109913936</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543315</v>
+        <v>543259</v>
       </c>
       <c r="R17" t="n">
-        <v>6966437</v>
+        <v>6966422</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109913959</v>
+        <v>109913955</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543102</v>
+        <v>543315</v>
       </c>
       <c r="R18" t="n">
-        <v>6966329</v>
+        <v>6966437</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109913939</v>
+        <v>109913959</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543259</v>
+        <v>543102</v>
       </c>
       <c r="R19" t="n">
-        <v>6966422</v>
+        <v>6966329</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2421,45 +2421,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109913940</v>
+        <v>135533945</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalberget, Jmt</t>
+          <t>Tallskogen, Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543268</v>
+        <v>543390</v>
       </c>
       <c r="R20" t="n">
-        <v>6966603</v>
+        <v>6966482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2506,57 +2506,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109913961</v>
+        <v>135533946</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skalberget, Jmt</t>
+          <t>Tallskogen, Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543135</v>
+        <v>543315</v>
       </c>
       <c r="R21" t="n">
-        <v>6966325</v>
+        <v>6966528</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2603,57 +2603,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109913934</v>
+        <v>135533947</v>
       </c>
       <c r="B22" t="n">
-        <v>79413</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skalberget, Jmt</t>
+          <t>Tallskogen, Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543189</v>
+        <v>543194</v>
       </c>
       <c r="R22" t="n">
-        <v>6966423</v>
+        <v>6966327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2700,22 +2700,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109913937</v>
+        <v>109913939</v>
       </c>
       <c r="B23" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109913943</v>
+        <v>109913940</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109913956</v>
+        <v>109913961</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543022</v>
+        <v>543135</v>
       </c>
       <c r="R25" t="n">
-        <v>6966513</v>
+        <v>6966325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109888420</v>
+        <v>109913934</v>
       </c>
       <c r="B26" t="n">
-        <v>80432</v>
+        <v>79413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543030</v>
+        <v>543189</v>
       </c>
       <c r="R26" t="n">
-        <v>6966641</v>
+        <v>6966423</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3088,44 +3088,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109913949</v>
+        <v>109913937</v>
       </c>
       <c r="B27" t="n">
-        <v>80461</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543346</v>
+        <v>543259</v>
       </c>
       <c r="R27" t="n">
-        <v>6966508</v>
+        <v>6966422</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109888418</v>
+        <v>109913943</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,38 +3208,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542989</v>
+        <v>543268</v>
       </c>
       <c r="R28" t="n">
-        <v>6966621</v>
+        <v>6966603</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3266,17 +3262,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>några år gammalt ringhack</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3291,22 +3282,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109888419</v>
+        <v>109913956</v>
       </c>
       <c r="B29" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3314,21 +3305,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3338,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542965</v>
+        <v>543022</v>
       </c>
       <c r="R29" t="n">
-        <v>6966627</v>
+        <v>6966513</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3388,22 +3379,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109888422</v>
+        <v>109888420</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3411,21 +3402,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3435,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543045</v>
+        <v>543030</v>
       </c>
       <c r="R30" t="n">
-        <v>6966690</v>
+        <v>6966641</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3497,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109913938</v>
+        <v>109913949</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3532,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543259</v>
+        <v>543346</v>
       </c>
       <c r="R31" t="n">
-        <v>6966422</v>
+        <v>6966508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3594,10 +3585,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109913941</v>
+        <v>109888418</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3605,34 +3596,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543268</v>
+        <v>542989</v>
       </c>
       <c r="R32" t="n">
-        <v>6966603</v>
+        <v>6966621</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3659,12 +3654,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>några år gammalt ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3679,19 +3679,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109913957</v>
+        <v>109888419</v>
       </c>
       <c r="B33" t="n">
         <v>79085</v>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543022</v>
+        <v>542965</v>
       </c>
       <c r="R33" t="n">
-        <v>6966513</v>
+        <v>6966627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3776,22 +3776,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109913926</v>
+        <v>109888422</v>
       </c>
       <c r="B34" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3799,21 +3799,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543159</v>
+        <v>543045</v>
       </c>
       <c r="R34" t="n">
-        <v>6966350</v>
+        <v>6966690</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3873,22 +3873,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109913942</v>
+        <v>109913938</v>
       </c>
       <c r="B35" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3896,21 +3896,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543268</v>
+        <v>543259</v>
       </c>
       <c r="R35" t="n">
-        <v>6966603</v>
+        <v>6966422</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,10 +3982,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109913960</v>
+        <v>109913941</v>
       </c>
       <c r="B36" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3993,21 +3993,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4017,10 +4017,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543135</v>
+        <v>543268</v>
       </c>
       <c r="R36" t="n">
-        <v>6966325</v>
+        <v>6966603</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4076,6 +4076,394 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>109913957</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>543022</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6966513</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>109913926</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>543159</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6966350</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>109913942</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>543268</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6966603</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>109913960</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>543135</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6966325</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913951</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913928</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913933</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913954</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913958</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913947</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913950</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913929</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913935</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913953</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913931</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135533943</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913948</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109888421</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913936</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913955</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913959</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135533945</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135533946</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135533947</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913939</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913940</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913961</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913934</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913937</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913943</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913956</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109888420</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913949</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3688,6 +3843,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109888418</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3785,6 +3945,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109888419</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3882,6 +4047,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109888422</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3979,6 +4149,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913938</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4076,6 +4251,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913941</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4173,6 +4353,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913957</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4270,6 +4455,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913926</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4367,6 +4557,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913942</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4464,8 +4659,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913960</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>135533943</v>
       </c>
       <c r="B14" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135533945</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135533946</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>135533947</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>135533943</v>
       </c>
       <c r="B14" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135533945</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135533946</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>135533947</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1904,45 +1904,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109913948</v>
+        <v>135533943</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>92069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skalberget, Jmt</t>
+          <t>Tallskogen, Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543329</v>
+        <v>543200</v>
       </c>
       <c r="R14" t="n">
-        <v>6966529</v>
+        <v>6966382</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,49 +1989,49 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913948</t>
+          <t>https://artportalen.se/Sighting/135533943</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109888421</v>
+        <v>109913948</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543045</v>
+        <v>543329</v>
       </c>
       <c r="R15" t="n">
-        <v>6966690</v>
+        <v>6966529</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,24 +2091,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109888421</t>
+          <t>https://artportalen.se/Sighting/109913948</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109913936</v>
+        <v>109888421</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543259</v>
+        <v>543045</v>
       </c>
       <c r="R16" t="n">
-        <v>6966422</v>
+        <v>6966690</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2193,24 +2193,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913936</t>
+          <t>https://artportalen.se/Sighting/109888421</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109913955</v>
+        <v>109913936</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543315</v>
+        <v>543259</v>
       </c>
       <c r="R17" t="n">
-        <v>6966437</v>
+        <v>6966422</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,13 +2306,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913955</t>
+          <t>https://artportalen.se/Sighting/109913936</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109913959</v>
+        <v>109913955</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543102</v>
+        <v>543315</v>
       </c>
       <c r="R18" t="n">
-        <v>6966329</v>
+        <v>6966437</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2408,38 +2408,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913959</t>
+          <t>https://artportalen.se/Sighting/109913955</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109913939</v>
+        <v>109913959</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543259</v>
+        <v>543102</v>
       </c>
       <c r="R19" t="n">
-        <v>6966422</v>
+        <v>6966329</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2510,51 +2510,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913939</t>
+          <t>https://artportalen.se/Sighting/109913959</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109913940</v>
+        <v>135533945</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skalberget, Jmt</t>
+          <t>Tallskogen, Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543268</v>
+        <v>543390</v>
       </c>
       <c r="R20" t="n">
-        <v>6966603</v>
+        <v>6966482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2601,62 +2601,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913940</t>
+          <t>https://artportalen.se/Sighting/135533945</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109913961</v>
+        <v>135533946</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skalberget, Jmt</t>
+          <t>Tallskogen, Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543135</v>
+        <v>543315</v>
       </c>
       <c r="R21" t="n">
-        <v>6966325</v>
+        <v>6966528</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2703,62 +2703,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913961</t>
+          <t>https://artportalen.se/Sighting/135533946</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109913934</v>
+        <v>135533947</v>
       </c>
       <c r="B22" t="n">
-        <v>79413</v>
+        <v>79441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skalberget, Jmt</t>
+          <t>Tallskogen, Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543189</v>
+        <v>543194</v>
       </c>
       <c r="R22" t="n">
-        <v>6966423</v>
+        <v>6966327</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2805,27 +2805,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Carl A Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913934</t>
+          <t>https://artportalen.se/Sighting/135533947</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109913937</v>
+        <v>109913939</v>
       </c>
       <c r="B23" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,16 +2918,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913937</t>
+          <t>https://artportalen.se/Sighting/109913939</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109913943</v>
+        <v>109913940</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3020,16 +3020,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913943</t>
+          <t>https://artportalen.se/Sighting/109913940</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109913956</v>
+        <v>109913961</v>
       </c>
       <c r="B25" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543022</v>
+        <v>543135</v>
       </c>
       <c r="R25" t="n">
-        <v>6966513</v>
+        <v>6966325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,16 +3122,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913956</t>
+          <t>https://artportalen.se/Sighting/109913961</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109888420</v>
+        <v>109913934</v>
       </c>
       <c r="B26" t="n">
-        <v>80432</v>
+        <v>79413</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543030</v>
+        <v>543189</v>
       </c>
       <c r="R26" t="n">
-        <v>6966641</v>
+        <v>6966423</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,49 +3213,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109888420</t>
+          <t>https://artportalen.se/Sighting/109913934</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109913949</v>
+        <v>109913937</v>
       </c>
       <c r="B27" t="n">
-        <v>80461</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543346</v>
+        <v>543259</v>
       </c>
       <c r="R27" t="n">
-        <v>6966508</v>
+        <v>6966422</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3326,16 +3326,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913949</t>
+          <t>https://artportalen.se/Sighting/109913937</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109888418</v>
+        <v>109913943</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3343,38 +3343,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542989</v>
+        <v>543268</v>
       </c>
       <c r="R28" t="n">
-        <v>6966621</v>
+        <v>6966603</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,17 +3397,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>några år gammalt ringhack</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3426,27 +3417,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109888418</t>
+          <t>https://artportalen.se/Sighting/109913943</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109888419</v>
+        <v>109913956</v>
       </c>
       <c r="B29" t="n">
-        <v>79085</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3454,21 +3445,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3478,10 +3469,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542965</v>
+        <v>543022</v>
       </c>
       <c r="R29" t="n">
-        <v>6966627</v>
+        <v>6966513</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,27 +3519,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Edith Bremer Storm</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109888419</t>
+          <t>https://artportalen.se/Sighting/109913956</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109888422</v>
+        <v>109888420</v>
       </c>
       <c r="B30" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,21 +3547,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3571,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543045</v>
+        <v>543030</v>
       </c>
       <c r="R30" t="n">
-        <v>6966690</v>
+        <v>6966641</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3641,38 +3632,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109888422</t>
+          <t>https://artportalen.se/Sighting/109888420</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109913938</v>
+        <v>109913949</v>
       </c>
       <c r="B31" t="n">
-        <v>79085</v>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3682,10 +3673,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543259</v>
+        <v>543346</v>
       </c>
       <c r="R31" t="n">
-        <v>6966422</v>
+        <v>6966508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,16 +3734,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913938</t>
+          <t>https://artportalen.se/Sighting/109913949</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109913941</v>
+        <v>109888418</v>
       </c>
       <c r="B32" t="n">
-        <v>79085</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3760,34 +3751,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Skalberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543268</v>
+        <v>542989</v>
       </c>
       <c r="R32" t="n">
-        <v>6966603</v>
+        <v>6966621</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,12 +3809,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>några år gammalt ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3834,24 +3834,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913941</t>
+          <t>https://artportalen.se/Sighting/109888418</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109913957</v>
+        <v>109888419</v>
       </c>
       <c r="B33" t="n">
         <v>79085</v>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543022</v>
+        <v>542965</v>
       </c>
       <c r="R33" t="n">
-        <v>6966513</v>
+        <v>6966627</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,27 +3936,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913957</t>
+          <t>https://artportalen.se/Sighting/109888419</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109913926</v>
+        <v>109888422</v>
       </c>
       <c r="B34" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3964,21 +3964,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3988,10 +3988,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543159</v>
+        <v>543045</v>
       </c>
       <c r="R34" t="n">
-        <v>6966350</v>
+        <v>6966690</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4018,12 +4018,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4038,27 +4038,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913926</t>
+          <t>https://artportalen.se/Sighting/109888422</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109913942</v>
+        <v>109913938</v>
       </c>
       <c r="B35" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543268</v>
+        <v>543259</v>
       </c>
       <c r="R35" t="n">
-        <v>6966603</v>
+        <v>6966422</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4151,16 +4151,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109913942</t>
+          <t>https://artportalen.se/Sighting/109913938</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109913960</v>
+        <v>109913941</v>
       </c>
       <c r="B36" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4168,21 +4168,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4192,10 +4192,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543135</v>
+        <v>543268</v>
       </c>
       <c r="R36" t="n">
-        <v>6966325</v>
+        <v>6966603</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4252,6 +4252,414 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913941</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>109913957</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>543022</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6966513</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913957</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>109913926</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>543159</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6966350</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913926</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>109913942</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>543268</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6966603</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-06-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109913942</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>109913960</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skalberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>543135</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6966325</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-06-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/109913960</t>
         </is>
@@ -4294,6 +4702,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>135533943</v>
       </c>
       <c r="B14" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>135533943</v>
       </c>
       <c r="B14" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135533945</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135533946</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>135533947</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 49645-2023 artfynd.xlsx
+++ b/artfynd/A 49645-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>135533943</v>
       </c>
       <c r="B14" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>135533945</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>135533946</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>135533947</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
